--- a/rod_hotels_audit_dataprep.xlsx
+++ b/rod_hotels_audit_dataprep.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -612,6 +612,24 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ML strict (remove partial missing)</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>52</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-10</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>10 colonnes avec NA supprimées</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rod_hotels_audit_dataprep.xlsx
+++ b/rod_hotels_audit_dataprep.xlsx
@@ -547,14 +547,14 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="C7" t="n">
-        <v>-15</v>
+        <v>-4</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>15 colonnes supprimées par pattern métier</t>
+          <t>4 colonnes supprimées par pattern métier</t>
         </is>
       </c>
     </row>
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -583,14 +583,14 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="C9" t="n">
-        <v>-17</v>
+        <v>-19</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>17 colonnes constantes supprimées</t>
+          <t>19 colonnes constantes supprimées</t>
         </is>
       </c>
     </row>
@@ -601,10 +601,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="C10" t="n">
-        <v>-82</v>
+        <v>-73</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -619,14 +619,14 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C11" t="n">
-        <v>-10</v>
+        <v>-18</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>10 colonnes avec NA supprimées</t>
+          <t>18 colonnes avec NA supprimées</t>
         </is>
       </c>
     </row>
